--- a/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -526,7 +526,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -548,7 +548,7 @@
     <t>QuestionnaireResponse.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|Procedure) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/procedure-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -636,7 +636,7 @@
 Focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/location-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -664,7 +664,7 @@
     <t>QuestionnaireResponse.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -729,7 +729,7 @@
 ServicePractitionerDepartmentCompanyPerformer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Practitioner|PractitionerRole|Patient|RelatedPerson|Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -757,7 +757,7 @@
     <t>QuestionnaireResponse.source</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1290,7 +1290,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="118.265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-questionnaireresponse-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
